--- a/output/codebook.xlsx
+++ b/output/codebook.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -41,7 +41,7 @@
     <t xml:space="preserve">POSIXct</t>
   </si>
   <si>
-    <t xml:space="preserve">[1.78834e+09, 1.78834e+09]</t>
+    <t xml:space="preserve">[1.79015e+09, 1.79015e+09]</t>
   </si>
   <si>
     <t xml:space="preserve"/>
@@ -59,12 +59,6 @@
     <t xml:space="preserve">IP Address</t>
   </si>
   <si>
-    <t xml:space="preserve">IPAddress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.132.173.28</t>
-  </si>
-  <si>
     <t xml:space="preserve">Progress</t>
   </si>
   <si>
@@ -77,7 +71,7 @@
     <t xml:space="preserve">Durationinseconds</t>
   </si>
   <si>
-    <t xml:space="preserve">[27, 131]</t>
+    <t xml:space="preserve">[14, 120]</t>
   </si>
   <si>
     <t xml:space="preserve">Finished</t>
@@ -92,19 +86,7 @@
     <t xml:space="preserve">responseid</t>
   </si>
   <si>
-    <t xml:space="preserve">R_3n0dq8SaplSWUvS | R_3tR6jXFUv1zT4yZ | R_6uOqS4vEPTjXh9e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LocationLatitude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[41.3186, 41.3186]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LocationLongitude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-72.9302, -72.9302]</t>
+    <t xml:space="preserve">R_1gSJxBmH07l3A8u | R_3Pw8eqtaKwkReOR</t>
   </si>
   <si>
     <t xml:space="preserve">DistributionChannel</t>
@@ -116,13 +98,13 @@
     <t xml:space="preserve">Q_RecaptchaScore</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8999999761581421</t>
+    <t xml:space="preserve">[1, 1]</t>
   </si>
   <si>
     <t xml:space="preserve">Q_DuplicateRespondent</t>
   </si>
   <si>
-    <t xml:space="preserve">true</t>
+    <t xml:space="preserve"> | true</t>
   </si>
   <si>
     <t xml:space="preserve">LastSeenFlowElementID</t>
@@ -134,177 +116,108 @@
     <t xml:space="preserve">LastSeenQuestionIDs</t>
   </si>
   <si>
-    <t xml:space="preserve">metadata_Browser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chrome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metadata_Version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.0.0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metadata_OperatingSystem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windows NT 10.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metadata_Resolution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1920x1080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prolific_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1, 3]</t>
-  </si>
-  <si>
     <t xml:space="preserve">colors</t>
   </si>
   <si>
-    <t xml:space="preserve">I encountered an error doing what you asked. Could you try again? | red and brown</t>
+    <t xml:space="preserve">Red,Brown | Red,Green</t>
   </si>
   <si>
     <t xml:space="preserve">video_5</t>
   </si>
   <si>
+    <t xml:space="preserve">[1, 5]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">video_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2, 2]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">video_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[3, 4]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">video_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">video_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">time</t>
+  </si>
+  <si>
     <t xml:space="preserve">[5, 5]</t>
   </si>
   <si>
-    <t xml:space="preserve">video_7</t>
+    <t xml:space="preserve">showup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dict_top_option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">npage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[3, 3]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tracking_json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[{"page":1,"question_ids":["QID45"],"start_time":1790175175958,"time_on_page":2,"mouse_moved":true,"mouse_move_count":73,"click_count":0,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"tab_switches":[],"scroll_event_count":10,"event_log":[],"ts":1790175177660},{"page":2,"question_ids":["QID21"],"start_time":1790175177889,"time_on_page":4,"mouse_moved":true,"mouse_move_count":61,"click_count":0,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"tab_switches":[],"scroll_event_count":0,"event_log":[],"ts":1790175182105},{"page":3,"question_ids":["QID50"],"start_time":1790175182394,"time_on_page":3,"mouse_moved":true,"mouse_move_count":113,"click_count":4,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"tab_switches":[],"scroll_event_count":11,"event_log":[],"ts":1790175185353},{"page":4,"question_ids":["QID48"],"start_time":1790175185672,"time_on_page":3,"mouse_moved":true,"mouse_move_count":135,"click_count":0,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"tab_switches":[],"scroll_event_count":9,"event_log":[],"ts":1790175188863},{"page":5,"question_ids":["QID51"],"start_time":1790175189049,"time_on_page":2,"mouse_moved":true,"mouse_move_count":45,"click_count":1,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"tab_switches":[],"scroll_event_count":1,"event_log":[],"ts":1790175190587}] | [{"page":1,"question_ids":["QID45"],"start_time":1790175193751,"time_on_page":1,"mouse_moved":true,"mouse_move_count":71,"click_count":0,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"tab_switches":[],"scroll_event_count":10,"event_log":[],"ts":1790175195202},{"page":2,"question_ids":["QID21"],"start_time":1790175195489,"time_on_page":5,"mouse_moved":true,"mouse_move_count":58,"click_count":0,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"tab_switches":[],"scroll_event_count":0,"event_log":[],"ts":1790175200203},{"page":3,"question_ids":["QID50"],"start_time":1790175200573,"time_on_page":109,"mouse_moved":true,"mouse_move_count":110,"click_count":4,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":true,"tab_switches":[{"start":649,"ms":105790}],"scroll_event_count":12,"event_log":[],"ts":1790175309873},{"page":4,"question_ids":["QID48"],"start_time":1790175310103,"time_on_page":2,"mouse_moved":true,"mouse_move_count":77,"click_count":0,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"tab_switches":[],"scroll_event_count":12,"event_log":[],"ts":1790175312249},{"page":5,"question_ids":["QID52"],"start_time":1790175312692,"time_on_page":1,"mouse_moved":true,"mouse_move_count":32,"click_count":0,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"tab_switches":[],"scroll_event_count":1,"event_log":[],"ts":1790175313711}]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[6, 6]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prolific</t>
+  </si>
+  <si>
+    <t xml:space="preserve">day_of_month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[23, 23]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[9, 9]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exclusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0, 0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">consent_page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">consent_duration</t>
   </si>
   <si>
     <t xml:space="preserve">[1, 2]</t>
   </si>
   <si>
-    <t xml:space="preserve">video_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[3, 3]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">video_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">video_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[4, 4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">showup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1, 1]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dict_top_option</t>
-  </si>
-  <si>
-    <t xml:space="preserve">npage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROLIFIC_PID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STUDY_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SESSION_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tracking_json</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[{"page":1,"question_ids":["QID45","QID43"],"start_time":1788364779735,"time_on_page":1,"mouse_moved":true,"mouse_move_count":53,"click_count":0,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"window_blurred":false,"scroll_event_count":12,"event_log":[],"ts":1788364781063},{"page":2,"question_ids":["QID47"],"start_time":1788364781293,"time_on_page":3,"mouse_moved":true,"mouse_move_count":49,"click_count":1,"total_keys":5,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"window_blurred":false,"scroll_event_count":1,"event_log":[],"ts":1788364784451},{"page":3,"question_ids":["QID21"],"start_time":1788364784578,"time_on_page":12,"mouse_moved":true,"mouse_move_count":128,"click_count":1,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"window_blurred":true,"scroll_event_count":0,"event_log":[{"event":"WINDOW_BLUR","time":1788364785603},{"event":"WINDOW_FOCUS","time":1788364785889},{"event":"WINDOW_BLUR","time":1788364785889},{"event":"WINDOW_FOCUS","time":1788364793043},{"event":"WINDOW_BLUR","time":1788364793083},{"event":"WINDOW_FOCUS","time":1788364794465},{"event":"WINDOW_BLUR","time":1788364794465},{"event":"WINDOW_FOCUS","time":1788364796005},{"event":"WINDOW_BLUR","time":1788364796005},{"event":"WINDOW_FOCUS","time":1788364796794}],"ts":1788364796871},{"page":4,"question_ids":["QID50"],"start_time":1788364797170,"time_on_page":4,"mouse_moved":true,"mouse_move_count":61,"click_count":1,"total_keys":13,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"window_blurred":false,"scroll_event_count":11,"event_log":[],"ts":1788364800765},{"page":5,"question_ids":["QID48"],"start_time":1788364800915,"time_on_page":4,"mouse_moved":true,"mouse_move_count":164,"click_count":0,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"window_blurred":false,"scroll_event_count":56,"event_log":[],"ts":1788364805361},{"page":6,"question_ids":["QID51"],"start_time":1788364805834,"time_on_page":1,"mouse_moved":true,"mouse_move_count":36,"click_count":0,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"window_blurred":false,"scroll_event_count":1,"event_log":[],"ts":1788364806911}] | [{"page":1,"question_ids":["QID45","QID43"],"start_time":1788364812730,"time_on_page":2,"mouse_moved":true,"mouse_move_count":56,"click_count":0,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"window_blurred":false,"scroll_event_count":12,"event_log":[],"ts":1788364814815},{"page":2,"question_ids":["QID47"],"start_time":1788364815302,"time_on_page":2,"mouse_moved":true,"mouse_move_count":65,"click_count":1,"total_keys":1,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"window_blurred":false,"scroll_event_count":1,"event_log":[],"ts":1788364817415},{"page":3,"question_ids":["QID21"],"start_time":1788364817760,"time_on_page":8,"mouse_moved":true,"mouse_move_count":119,"click_count":0,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":true,"window_blurred":true,"scroll_event_count":0,"event_log":[{"event":"WINDOW_BLUR","time":1788364818717},{"event":"TAB_HIDDEN","time":1788364822065},{"event":"WINDOW_BLUR","time":1788364822708},{"event":"TAB_VISIBLE","time":1788364824008},{"event":"WINDOW_FOCUS","time":1788364825439}],"ts":1788364825574},{"page":4,"question_ids":["QID50"],"start_time":1788364825823,"time_on_page":108,"mouse_moved":true,"mouse_move_count":557,"click_count":13,"total_keys":9,"paste_detected":true,"copy_detected":true,"tab_hidden":true,"window_blurred":true,"scroll_event_count":0,"event_log":[{"event":"COPY","time":1788364828373},{"event":"WINDOW_BLUR","time":1788364828761},{"event":"TAB_HIDDEN","time":1788364828767},{"event":"TAB_VISIBLE","time":1788364842819},{"event":"WINDOW_FOCUS","time":1788364842820},{"event":"WINDOW_BLUR","time":1788364845568},{"event":"TAB_HIDDEN","time":1788364845573},{"event":"TAB_VISIBLE","time":1788364847549},{"event":"WINDOW_FOCUS","time":1788364847550},{"event":"COPY","time":1788364850807},{"event":"COPY","time":1788364854586},{"event":"WINDOW_BLUR","time":1788364855888},{"event":"TAB_HIDDEN","time":1788364855892},{"event":"TAB_VISIBLE","time":1788364866061},{"event":"WINDOW_FOCUS","time":1788364866062},{"event":"WINDOW_BLUR","time":1788364867625},{"event":"TAB_HIDDEN","time":1788364867630},{"event":"TAB_VISIBLE","time":1788364887120},{"event":"WINDOW_FOCUS","time":1788364887122},{"event":"WINDOW_BLUR","time":1788364888071},{"event":"TAB_HIDDEN","time":1788364888074},{"event":"TAB_VISIBLE","time":1788364907422},{"event":"WINDOW_FOCUS","time":1788364907424},{"event":"WINDOW_BLUR","time":1788364908396},{"event":"TAB_HIDDEN","time":1788364908399},{"event":"TAB_VISIBLE","time":1788364926476},{"event":"WINDOW_FOCUS","time":1788364926477},{"event":"WINDOW_BLUR","time":1788364929501},{"event":"TAB_HIDDEN","time":1788364929505},{"event":"TAB_VISIBLE","time":1788364931584},{"event":"WINDOW_FOCUS","time":1788364931585},{"event":"PASTE","time":1788364932529}],"ts":1788364933652},{"page":5,"question_ids":["QID48"],"start_time":1788364933877,"time_on_page":8,"mouse_moved":true,"mouse_move_count":219,"click_count":1,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"window_blurred":false,"scroll_event_count":84,"event_log":[],"ts":1788364941489},{"page":6,"question_ids":["QID52"],"start_time":1788364941644,"time_on_page":3,"mouse_moved":true,"mouse_move_count":41,"click_count":0,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"window_blurred":false,"scroll_event_count":1,"event_log":[],"ts":1788364944145}] | [{"page":1,"question_ids":["QID45","QID43"],"start_time":1788364958159,"time_on_page":2,"mouse_moved":true,"mouse_move_count":65,"click_count":0,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"window_blurred":false,"scroll_event_count":22,"event_log":[],"ts":1788364959956},{"page":2,"question_ids":["QID47"],"start_time":1788364960192,"time_on_page":2,"mouse_moved":true,"mouse_move_count":76,"click_count":1,"total_keys":1,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"window_blurred":false,"scroll_event_count":1,"event_log":[],"ts":1788364962655},{"page":3,"question_ids":["QID21"],"start_time":1788364963072,"time_on_page":9,"mouse_moved":true,"mouse_move_count":66,"click_count":0,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"window_blurred":true,"scroll_event_count":0,"event_log":[{"event":"WINDOW_BLUR","time":1788364964010},{"event":"WINDOW_FOCUS","time":1788364964309},{"event":"WINDOW_BLUR","time":1788364964309},{"event":"WINDOW_FOCUS","time":1788364970090},{"event":"WINDOW_BLUR","time":1788364970090},{"event":"WINDOW_FOCUS","time":1788364972145}],"ts":1788364972225},{"page":4,"question_ids":["QID50"],"start_time":1788364972588,"time_on_page":10,"mouse_moved":true,"mouse_move_count":149,"click_count":2,"total_keys":2,"paste_detected":true,"copy_detected":false,"tab_hidden":true,"window_blurred":true,"scroll_event_count":11,"event_log":[{"event":"WINDOW_BLUR","time":1788364975320},{"event":"TAB_HIDDEN","time":1788364975323},{"event":"TAB_VISIBLE","time":1788364979962},{"event":"WINDOW_FOCUS","time":1788364979964},{"event":"PASTE","time":1788364981018}],"ts":1788364982229},{"page":5,"question_ids":["QID48"],"start_time":1788364982679,"time_on_page":40,"mouse_moved":true,"mouse_move_count":377,"click_count":1,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"window_blurred":false,"scroll_event_count":99,"event_log":[],"ts":1788365022715},{"page":6,"question_ids":["QID52"],"start_time":1788365022881,"time_on_page":3,"mouse_moved":true,"mouse_move_count":36,"click_count":0,"total_keys":0,"paste_detected":false,"copy_detected":false,"tab_hidden":false,"window_blurred":false,"scroll_event_count":1,"event_log":[],"ts":1788365026173}]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitorId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">msvaHSJoPXanfafy0raq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">requestId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1788364779253.WAVDT4 | 1788364812218.49TKLd | 1788364957667.GnjO7A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fp_error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ip_address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[7, 7]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key_log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[{"key":"Control","time":1788364828171},{"key":"c","time":1788364828373},{"key":"Control","time":1788364844417},{"key":"Control","time":1788364850560},{"key":"c","time":1788364850807},{"key":"Control","time":1788364854430},{"key":"c","time":1788364854586},{"key":"Control","time":1788364932484},{"key":"v","time":1788364932528}] | [{"key":"Control","time":1788364980949},{"key":"v","time":1788364981017}] | [{"key":"r","time":1788364798291},{"key":"e","time":1788364798336},{"key":"d","time":1788364798538},{"key":" ","time":1788364798651},{"key":"a","time":1788364798741},{"key":"n","time":1788364798808},{"key":"d","time":1788364798898},{"key":" ","time":1788364798944},{"key":"b","time":1788364799078},{"key":"r","time":1788364799213},{"key":"o","time":1788364799235},{"key":"w","time":1788364799371},{"key":"n","time":1788364799461}]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key_log2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prolific</t>
-  </si>
-  <si>
-    <t xml:space="preserve">day_of_month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">integer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[2, 2]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[9, 9]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exclusion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0, 0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">participant_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flag_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">consent_page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">consent_duration</t>
-  </si>
-  <si>
     <t xml:space="preserve">consent_paste</t>
   </si>
   <si>
@@ -320,147 +233,150 @@
     <t xml:space="preserve">consent_tab</t>
   </si>
   <si>
-    <t xml:space="preserve">consent_blur</t>
+    <t xml:space="preserve">consent_tabCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">consent_tabTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">consent_tabDurations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all missing</t>
   </si>
   <si>
     <t xml:space="preserve">consent_mouseMoveCount</t>
   </si>
   <si>
-    <t xml:space="preserve">[53, 65]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prolific_id_page</t>
+    <t xml:space="preserve">[71, 73]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">captcha_page</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">prolific_id_duration</t>
+    <t xml:space="preserve">captcha_duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[4, 5]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">captcha_paste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">captcha_copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">captcha_tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">captcha_tabCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">captcha_tabTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">captcha_tabDurations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">captcha_mouseMoveCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[58, 61]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colors_page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colors_duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[3, 109]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colors_paste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colors_copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colors_tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FALSE | TRUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colors_tabCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0, 1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colors_tabTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0, 105.79]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colors_tabDurations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colors_mouseMoveCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[110, 113]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">video_page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">video_duration</t>
   </si>
   <si>
     <t xml:space="preserve">[2, 3]</t>
   </si>
   <si>
-    <t xml:space="preserve">prolific_id_paste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prolific_id_copy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prolific_id_tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prolific_id_blur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prolific_id_mouseMoveCount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[49, 76]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">captcha_page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">captcha_duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[8, 12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">captcha_paste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">captcha_copy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">captcha_tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FALSE | TRUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">captcha_blur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">captcha_mouseMoveCount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[66, 128]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">colors_page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">colors_duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[4, 108]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">colors_paste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">colors_copy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">colors_tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">colors_blur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">colors_mouseMoveCount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[61, 557]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">video_page</t>
+    <t xml:space="preserve">video_paste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">video_copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">video_tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">video_tabCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">video_tabTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">video_tabDurations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">video_mouseMoveCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[77, 135]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q23_page</t>
   </si>
   <si>
     <t xml:space="preserve">5</t>
   </si>
   <si>
-    <t xml:space="preserve">video_duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[4, 40]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">video_paste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">video_copy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">video_tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">video_blur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">video_mouseMoveCount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[164, 377]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q23_page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q23_duration</t>
   </si>
   <si>
@@ -473,13 +389,19 @@
     <t xml:space="preserve">Q23_tab</t>
   </si>
   <si>
-    <t xml:space="preserve">Q23_blur</t>
+    <t xml:space="preserve">Q23_tabCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q23_tabTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q23_tabDurations</t>
   </si>
   <si>
     <t xml:space="preserve">Q23_mouseMoveCount</t>
   </si>
   <si>
-    <t xml:space="preserve">[36, 36]</t>
+    <t xml:space="preserve">[45, 45]</t>
   </si>
   <si>
     <t xml:space="preserve">Q24_page</t>
@@ -497,82 +419,19 @@
     <t xml:space="preserve">Q24_tab</t>
   </si>
   <si>
-    <t xml:space="preserve">Q24_blur</t>
+    <t xml:space="preserve">Q24_tabCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q24_tabTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q24_tabDurations</t>
   </si>
   <si>
     <t xml:space="preserve">Q24_mouseMoveCount</t>
   </si>
   <si>
-    <t xml:space="preserve">[36, 41]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key_log_str</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control|c|Control|Control|c|Control|c|Control|v | Control|v | r|e|d| |a|n|d| |b|r|o|w|n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key_log_num</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[2, 13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key_log_mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[68, 13044.6]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key_log_median</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[68, 1935]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key_log_sd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[50.0808, 26766.7]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key_log_inputjump</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key_log_inputjump_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key_log_inputjump_sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key_log_inputjump_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">all missing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key_log_wordCount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[3, 12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key_log_charCount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[13, 65]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key_log_reconstructedInput</t>
-  </si>
-  <si>
-    <t xml:space="preserve">red and brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">key_log_levenshtein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0, 1]</t>
+    <t xml:space="preserve">[32, 32]</t>
   </si>
   <si>
     <t xml:space="preserve">text</t>
@@ -621,12 +480,6 @@
   </si>
   <si>
     <t xml:space="preserve">ok_typedspeed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flag_ip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ok_ip</t>
   </si>
   <si>
     <t xml:space="preserve">all_passed</t>
@@ -989,7 +842,7 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1012,7 +865,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1035,7 +888,7 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1055,10 +908,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1067,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
@@ -1075,13 +928,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1101,10 +954,10 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1124,10 +977,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1136,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
@@ -1144,22 +997,22 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
         <v>24</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
       </c>
       <c r="G9" t="s">
         <v>10</v>
@@ -1173,7 +1026,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -1193,10 +1046,10 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1216,10 +1069,10 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -1242,7 +1095,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -1265,7 +1118,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -1274,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="G14" t="s">
         <v>10</v>
@@ -1282,13 +1135,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1297,7 +1150,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G15" t="s">
         <v>10</v>
@@ -1305,22 +1158,22 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="s">
         <v>37</v>
-      </c>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="s">
-        <v>38</v>
       </c>
       <c r="G16" t="s">
         <v>10</v>
@@ -1328,22 +1181,22 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="s">
         <v>39</v>
-      </c>
-      <c r="B17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="s">
-        <v>10</v>
       </c>
       <c r="G17" t="s">
         <v>10</v>
@@ -1354,10 +1207,10 @@
         <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1377,10 +1230,10 @@
         <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1389,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G19" t="s">
         <v>10</v>
@@ -1397,13 +1250,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1412,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G20" t="s">
         <v>10</v>
@@ -1420,13 +1273,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1435,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G21" t="s">
         <v>10</v>
@@ -1443,13 +1296,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1458,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="G22" t="s">
         <v>10</v>
@@ -1466,13 +1319,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1481,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="G23" t="s">
         <v>10</v>
@@ -1489,13 +1342,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1504,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G24" t="s">
         <v>10</v>
@@ -1512,13 +1365,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1527,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G25" t="s">
         <v>10</v>
@@ -1535,13 +1388,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1550,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G26" t="s">
         <v>10</v>
@@ -1558,13 +1411,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1573,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="G27" t="s">
         <v>10</v>
@@ -1581,13 +1434,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1596,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G28" t="s">
         <v>10</v>
@@ -1604,13 +1457,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1619,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G29" t="s">
         <v>10</v>
@@ -1627,13 +1480,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1642,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G30" t="s">
         <v>10</v>
@@ -1650,13 +1503,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1665,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="G31" t="s">
         <v>10</v>
@@ -1673,22 +1526,22 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="s">
         <v>65</v>
-      </c>
-      <c r="B32" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="s">
-        <v>57</v>
       </c>
       <c r="G32" t="s">
         <v>10</v>
@@ -1699,10 +1552,10 @@
         <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1711,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="G33" t="s">
         <v>10</v>
@@ -1719,13 +1572,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1734,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="G34" t="s">
         <v>10</v>
@@ -1742,13 +1595,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1757,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="G35" t="s">
         <v>10</v>
@@ -1765,13 +1618,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" t="s">
         <v>69</v>
       </c>
-      <c r="B36" t="s">
-        <v>13</v>
-      </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1788,13 +1641,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1803,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G37" t="s">
         <v>10</v>
@@ -1811,13 +1664,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -1826,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G38" t="s">
         <v>10</v>
@@ -1837,19 +1690,19 @@
         <v>75</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s">
         <v>10</v>
@@ -1857,13 +1710,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -1872,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s">
         <v>10</v>
@@ -1880,13 +1733,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1895,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s">
         <v>10</v>
@@ -1903,13 +1756,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -1918,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G42" t="s">
         <v>10</v>
@@ -1926,13 +1779,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -1941,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="G43" t="s">
         <v>10</v>
@@ -1949,13 +1802,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B44" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -1964,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="G44" t="s">
         <v>10</v>
@@ -1972,13 +1825,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -1987,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="G45" t="s">
         <v>10</v>
@@ -1995,13 +1848,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B46" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2010,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="F46" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="G46" t="s">
         <v>10</v>
@@ -2018,13 +1871,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B47" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -2033,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="G47" t="s">
         <v>10</v>
@@ -2041,22 +1894,22 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F48" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G48" t="s">
         <v>10</v>
@@ -2064,13 +1917,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -2079,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s">
         <v>10</v>
@@ -2087,13 +1940,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B50" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2102,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G50" t="s">
         <v>10</v>
@@ -2110,22 +1963,22 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>93</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="s">
         <v>94</v>
-      </c>
-      <c r="B51" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" t="n">
-        <v>3</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="s">
-        <v>95</v>
       </c>
       <c r="G51" t="s">
         <v>10</v>
@@ -2133,13 +1986,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B52" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2148,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G52" t="s">
         <v>10</v>
@@ -2156,13 +2009,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B53" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2171,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="G53" t="s">
         <v>10</v>
@@ -2179,22 +2032,22 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B54" t="s">
+        <v>69</v>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="s">
         <v>98</v>
-      </c>
-      <c r="C54" t="n">
-        <v>3</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="s">
-        <v>99</v>
       </c>
       <c r="G54" t="s">
         <v>10</v>
@@ -2202,13 +2055,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2217,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G55" t="s">
         <v>10</v>
@@ -2225,22 +2078,22 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>101</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="s">
         <v>102</v>
-      </c>
-      <c r="B56" t="s">
-        <v>98</v>
-      </c>
-      <c r="C56" t="n">
-        <v>3</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="s">
-        <v>99</v>
       </c>
       <c r="G56" t="s">
         <v>10</v>
@@ -2251,16 +2104,16 @@
         <v>103</v>
       </c>
       <c r="B57" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F57" t="s">
         <v>104</v>
@@ -2274,10 +2127,10 @@
         <v>105</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2297,10 +2150,10 @@
         <v>107</v>
       </c>
       <c r="B59" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2320,10 +2173,10 @@
         <v>109</v>
       </c>
       <c r="B60" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -2332,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="G60" t="s">
         <v>10</v>
@@ -2340,13 +2193,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -2355,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="F61" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="G61" t="s">
         <v>10</v>
@@ -2363,13 +2216,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B62" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -2378,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="F62" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="G62" t="s">
         <v>10</v>
@@ -2386,13 +2239,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B63" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -2401,7 +2254,7 @@
         <v>0</v>
       </c>
       <c r="F63" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="G63" t="s">
         <v>10</v>
@@ -2409,13 +2262,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B64" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -2424,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="F64" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="G64" t="s">
         <v>10</v>
@@ -2435,10 +2288,10 @@
         <v>115</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -2447,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="F65" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="G65" t="s">
         <v>10</v>
@@ -2455,22 +2308,22 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B66" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F66" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="G66" t="s">
         <v>10</v>
@@ -2478,13 +2331,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B67" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -2493,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="F67" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="G67" t="s">
         <v>10</v>
@@ -2501,22 +2354,22 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>119</v>
+      </c>
+      <c r="B68" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>50</v>
+      </c>
+      <c r="F68" t="s">
         <v>120</v>
-      </c>
-      <c r="B68" t="s">
-        <v>98</v>
-      </c>
-      <c r="C68" t="n">
-        <v>3</v>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="s">
-        <v>99</v>
       </c>
       <c r="G68" t="s">
         <v>10</v>
@@ -2527,19 +2380,19 @@
         <v>121</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F69" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="G69" t="s">
         <v>10</v>
@@ -2547,22 +2400,22 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B70" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F70" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="G70" t="s">
         <v>10</v>
@@ -2570,22 +2423,22 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F71" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="G71" t="s">
         <v>10</v>
@@ -2593,22 +2446,22 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F72" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="G72" t="s">
         <v>10</v>
@@ -2616,22 +2469,22 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B73" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F73" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="G73" t="s">
         <v>10</v>
@@ -2639,22 +2492,22 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B74" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F74" t="s">
-        <v>122</v>
+        <v>63</v>
       </c>
       <c r="G74" t="s">
         <v>10</v>
@@ -2662,22 +2515,22 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B75" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F75" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="G75" t="s">
         <v>10</v>
@@ -2685,22 +2538,22 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B76" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F76" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G76" t="s">
         <v>10</v>
@@ -2708,22 +2561,22 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B77" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F77" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G77" t="s">
         <v>10</v>
@@ -2731,22 +2584,22 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B78" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F78" t="s">
-        <v>136</v>
+        <v>28</v>
       </c>
       <c r="G78" t="s">
         <v>10</v>
@@ -2754,22 +2607,22 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B79" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F79" t="s">
-        <v>138</v>
+        <v>70</v>
       </c>
       <c r="G79" t="s">
         <v>10</v>
@@ -2777,22 +2630,22 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B80" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F80" t="s">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="G80" t="s">
         <v>10</v>
@@ -2800,22 +2653,22 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B81" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F81" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="G81" t="s">
         <v>10</v>
@@ -2823,22 +2676,22 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B82" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F82" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="G82" t="s">
         <v>10</v>
@@ -2846,22 +2699,22 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B83" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F83" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="G83" t="s">
         <v>10</v>
@@ -2869,22 +2722,22 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B84" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F84" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="G84" t="s">
         <v>10</v>
@@ -2892,22 +2745,22 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B85" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F85" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G85" t="s">
         <v>10</v>
@@ -2915,22 +2768,22 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="F86" t="s">
-        <v>148</v>
+        <v>35</v>
       </c>
       <c r="G86" t="s">
         <v>10</v>
@@ -2938,22 +2791,22 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B87" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="F87" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="G87" t="s">
         <v>10</v>
@@ -2961,22 +2814,22 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B88" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="F88" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G88" t="s">
         <v>10</v>
@@ -2984,22 +2837,22 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B89" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="F89" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G89" t="s">
         <v>10</v>
@@ -3007,22 +2860,22 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B90" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="F90" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G90" t="s">
         <v>10</v>
@@ -3030,22 +2883,22 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B91" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="F91" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="G91" t="s">
         <v>10</v>
@@ -3053,22 +2906,22 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B92" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="F92" t="s">
-        <v>155</v>
+        <v>28</v>
       </c>
       <c r="G92" t="s">
         <v>10</v>
@@ -3076,22 +2929,22 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B93" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="C93" t="n">
         <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F93" t="s">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="G93" t="s">
         <v>10</v>
@@ -3099,22 +2952,22 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B94" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C94" t="n">
         <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F94" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G94" t="s">
         <v>10</v>
@@ -3122,22 +2975,22 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B95" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="C95" t="n">
         <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F95" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="G95" t="s">
         <v>10</v>
@@ -3145,22 +2998,22 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B96" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="C96" t="n">
         <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F96" t="s">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="G96" t="s">
         <v>10</v>
@@ -3168,22 +3021,22 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B97" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="C97" t="n">
         <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F97" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="G97" t="s">
         <v>10</v>
@@ -3191,22 +3044,22 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="C98" t="n">
         <v>2</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F98" t="s">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="G98" t="s">
         <v>10</v>
@@ -3214,22 +3067,22 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B99" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C99" t="n">
         <v>2</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F99" t="s">
-        <v>163</v>
+        <v>63</v>
       </c>
       <c r="G99" t="s">
         <v>10</v>
@@ -3237,13 +3090,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B100" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -3252,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="F100" t="s">
-        <v>165</v>
+        <v>28</v>
       </c>
       <c r="G100" t="s">
         <v>10</v>
@@ -3260,13 +3113,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="B101" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -3275,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="F101" t="s">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="G101" t="s">
         <v>10</v>
@@ -3283,13 +3136,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="B102" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -3298,676 +3151,9 @@
         <v>0</v>
       </c>
       <c r="F102" t="s">
-        <v>169</v>
+        <v>100</v>
       </c>
       <c r="G102" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>170</v>
-      </c>
-      <c r="B103" t="s">
-        <v>18</v>
-      </c>
-      <c r="C103" t="n">
-        <v>3</v>
-      </c>
-      <c r="D103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" t="s">
-        <v>171</v>
-      </c>
-      <c r="G103" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>172</v>
-      </c>
-      <c r="B104" t="s">
-        <v>18</v>
-      </c>
-      <c r="C104" t="n">
-        <v>2</v>
-      </c>
-      <c r="D104" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="F104" t="s">
-        <v>173</v>
-      </c>
-      <c r="G104" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>174</v>
-      </c>
-      <c r="B105" t="s">
-        <v>18</v>
-      </c>
-      <c r="C105" t="n">
-        <v>3</v>
-      </c>
-      <c r="D105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="s">
-        <v>91</v>
-      </c>
-      <c r="G105" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>175</v>
-      </c>
-      <c r="B106" t="s">
-        <v>18</v>
-      </c>
-      <c r="C106" t="n">
-        <v>3</v>
-      </c>
-      <c r="D106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" t="s">
-        <v>91</v>
-      </c>
-      <c r="G106" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>176</v>
-      </c>
-      <c r="B107" t="s">
-        <v>18</v>
-      </c>
-      <c r="C107" t="n">
-        <v>3</v>
-      </c>
-      <c r="D107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" t="s">
-        <v>91</v>
-      </c>
-      <c r="G107" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>177</v>
-      </c>
-      <c r="B108" t="s">
-        <v>98</v>
-      </c>
-      <c r="C108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" t="n">
-        <v>3</v>
-      </c>
-      <c r="E108" t="n">
-        <v>100</v>
-      </c>
-      <c r="F108" t="s">
-        <v>178</v>
-      </c>
-      <c r="G108" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>179</v>
-      </c>
-      <c r="B109" t="s">
-        <v>18</v>
-      </c>
-      <c r="C109" t="n">
-        <v>3</v>
-      </c>
-      <c r="D109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" t="s">
-        <v>180</v>
-      </c>
-      <c r="G109" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>181</v>
-      </c>
-      <c r="B110" t="s">
-        <v>18</v>
-      </c>
-      <c r="C110" t="n">
-        <v>3</v>
-      </c>
-      <c r="D110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" t="s">
-        <v>182</v>
-      </c>
-      <c r="G110" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>183</v>
-      </c>
-      <c r="B111" t="s">
-        <v>13</v>
-      </c>
-      <c r="C111" t="n">
-        <v>1</v>
-      </c>
-      <c r="D111" t="n">
-        <v>2</v>
-      </c>
-      <c r="E111" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F111" t="s">
-        <v>184</v>
-      </c>
-      <c r="G111" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>185</v>
-      </c>
-      <c r="B112" t="s">
-        <v>18</v>
-      </c>
-      <c r="C112" t="n">
-        <v>3</v>
-      </c>
-      <c r="D112" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" t="s">
-        <v>186</v>
-      </c>
-      <c r="G112" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>187</v>
-      </c>
-      <c r="B113" t="s">
-        <v>13</v>
-      </c>
-      <c r="C113" t="n">
-        <v>3</v>
-      </c>
-      <c r="D113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" t="s">
-        <v>51</v>
-      </c>
-      <c r="G113" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>188</v>
-      </c>
-      <c r="B114" t="s">
-        <v>86</v>
-      </c>
-      <c r="C114" t="n">
-        <v>3</v>
-      </c>
-      <c r="D114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" t="s">
-        <v>186</v>
-      </c>
-      <c r="G114" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>189</v>
-      </c>
-      <c r="B115" t="s">
-        <v>86</v>
-      </c>
-      <c r="C115" t="n">
-        <v>3</v>
-      </c>
-      <c r="D115" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" t="s">
-        <v>186</v>
-      </c>
-      <c r="G115" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>190</v>
-      </c>
-      <c r="B116" t="s">
-        <v>86</v>
-      </c>
-      <c r="C116" t="n">
-        <v>3</v>
-      </c>
-      <c r="D116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" t="s">
-        <v>186</v>
-      </c>
-      <c r="G116" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>191</v>
-      </c>
-      <c r="B117" t="s">
-        <v>86</v>
-      </c>
-      <c r="C117" t="n">
-        <v>3</v>
-      </c>
-      <c r="D117" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" t="s">
-        <v>186</v>
-      </c>
-      <c r="G117" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>192</v>
-      </c>
-      <c r="B118" t="s">
-        <v>86</v>
-      </c>
-      <c r="C118" t="n">
-        <v>3</v>
-      </c>
-      <c r="D118" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" t="s">
-        <v>91</v>
-      </c>
-      <c r="G118" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>193</v>
-      </c>
-      <c r="B119" t="s">
-        <v>86</v>
-      </c>
-      <c r="C119" t="n">
-        <v>3</v>
-      </c>
-      <c r="D119" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" t="s">
-        <v>63</v>
-      </c>
-      <c r="G119" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>194</v>
-      </c>
-      <c r="B120" t="s">
-        <v>86</v>
-      </c>
-      <c r="C120" t="n">
-        <v>3</v>
-      </c>
-      <c r="D120" t="n">
-        <v>0</v>
-      </c>
-      <c r="E120" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" t="s">
-        <v>186</v>
-      </c>
-      <c r="G120" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>195</v>
-      </c>
-      <c r="B121" t="s">
-        <v>86</v>
-      </c>
-      <c r="C121" t="n">
-        <v>3</v>
-      </c>
-      <c r="D121" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" t="s">
-        <v>186</v>
-      </c>
-      <c r="G121" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>196</v>
-      </c>
-      <c r="B122" t="s">
-        <v>86</v>
-      </c>
-      <c r="C122" t="n">
-        <v>3</v>
-      </c>
-      <c r="D122" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" t="s">
-        <v>91</v>
-      </c>
-      <c r="G122" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>197</v>
-      </c>
-      <c r="B123" t="s">
-        <v>86</v>
-      </c>
-      <c r="C123" t="n">
-        <v>3</v>
-      </c>
-      <c r="D123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" t="s">
-        <v>63</v>
-      </c>
-      <c r="G123" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>198</v>
-      </c>
-      <c r="B124" t="s">
-        <v>86</v>
-      </c>
-      <c r="C124" t="n">
-        <v>3</v>
-      </c>
-      <c r="D124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" t="s">
-        <v>186</v>
-      </c>
-      <c r="G124" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>199</v>
-      </c>
-      <c r="B125" t="s">
-        <v>86</v>
-      </c>
-      <c r="C125" t="n">
-        <v>3</v>
-      </c>
-      <c r="D125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" t="s">
-        <v>186</v>
-      </c>
-      <c r="G125" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>200</v>
-      </c>
-      <c r="B126" t="s">
-        <v>86</v>
-      </c>
-      <c r="C126" t="n">
-        <v>3</v>
-      </c>
-      <c r="D126" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" t="s">
-        <v>186</v>
-      </c>
-      <c r="G126" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>201</v>
-      </c>
-      <c r="B127" t="s">
-        <v>86</v>
-      </c>
-      <c r="C127" t="n">
-        <v>3</v>
-      </c>
-      <c r="D127" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" t="s">
-        <v>186</v>
-      </c>
-      <c r="G127" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>202</v>
-      </c>
-      <c r="B128" t="s">
-        <v>86</v>
-      </c>
-      <c r="C128" t="n">
-        <v>3</v>
-      </c>
-      <c r="D128" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" t="s">
-        <v>186</v>
-      </c>
-      <c r="G128" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>203</v>
-      </c>
-      <c r="B129" t="s">
-        <v>86</v>
-      </c>
-      <c r="C129" t="n">
-        <v>3</v>
-      </c>
-      <c r="D129" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" t="s">
-        <v>63</v>
-      </c>
-      <c r="G129" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>204</v>
-      </c>
-      <c r="B130" t="s">
-        <v>86</v>
-      </c>
-      <c r="C130" t="n">
-        <v>3</v>
-      </c>
-      <c r="D130" t="n">
-        <v>0</v>
-      </c>
-      <c r="E130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" t="s">
-        <v>91</v>
-      </c>
-      <c r="G130" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>205</v>
-      </c>
-      <c r="B131" t="s">
-        <v>86</v>
-      </c>
-      <c r="C131" t="n">
-        <v>3</v>
-      </c>
-      <c r="D131" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" t="s">
-        <v>91</v>
-      </c>
-      <c r="G131" t="s">
         <v>10</v>
       </c>
     </row>
